--- a/Files/Madden25/IE/Season10/ActivePlayerCounts.xlsx
+++ b/Files/Madden25/IE/Season10/ActivePlayerCounts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E650"/>
+  <dimension ref="A1:E652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -520,11 +520,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -539,11 +539,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -558,11 +558,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -577,11 +577,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -596,11 +596,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -615,11 +615,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -634,11 +634,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -653,11 +653,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -672,11 +672,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
@@ -691,11 +691,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -729,11 +729,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -767,11 +767,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -786,11 +786,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -805,11 +805,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -838,16 +838,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -862,11 +862,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -881,11 +881,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -900,11 +900,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" t="b">
         <v>0</v>
@@ -919,7 +919,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -938,11 +938,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -957,11 +957,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -976,11 +976,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -995,11 +995,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1052,11 +1052,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="b">
         <v>0</v>
@@ -1071,11 +1071,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="b">
         <v>0</v>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="b">
         <v>0</v>
@@ -1109,11 +1109,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="b">
         <v>0</v>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1147,11 +1147,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="b">
         <v>0</v>
@@ -1166,11 +1166,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="b">
         <v>0</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1204,11 +1204,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="b">
         <v>0</v>
@@ -1223,11 +1223,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D42" t="b">
         <v>0</v>
@@ -1237,16 +1237,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D43" t="b">
         <v>0</v>
@@ -1261,11 +1261,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D44" t="b">
         <v>0</v>
@@ -1280,11 +1280,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="b">
         <v>0</v>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="b">
         <v>0</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1337,11 +1337,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48" t="b">
         <v>0</v>
@@ -1356,11 +1356,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="b">
         <v>0</v>
@@ -1375,11 +1375,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="b">
         <v>0</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1451,11 +1451,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="b">
         <v>0</v>
@@ -1470,11 +1470,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" t="b">
         <v>0</v>
@@ -1489,11 +1489,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="b">
         <v>0</v>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="b">
         <v>0</v>
@@ -1527,11 +1527,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="b">
         <v>0</v>
@@ -1546,11 +1546,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="b">
         <v>0</v>
@@ -1565,11 +1565,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="b">
         <v>0</v>
@@ -1584,11 +1584,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="b">
         <v>0</v>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D62" t="b">
         <v>0</v>
@@ -1617,16 +1617,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D63" t="b">
         <v>0</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D64" t="b">
         <v>0</v>
@@ -1660,11 +1660,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D65" t="b">
         <v>0</v>
@@ -1679,11 +1679,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" t="b">
         <v>0</v>
@@ -1698,11 +1698,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67" t="b">
         <v>0</v>
@@ -1717,11 +1717,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" t="b">
         <v>0</v>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="b">
         <v>0</v>
@@ -1755,11 +1755,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70" t="b">
         <v>0</v>
@@ -1774,11 +1774,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="b">
         <v>0</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="b">
         <v>0</v>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="b">
         <v>0</v>
@@ -1850,11 +1850,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" t="b">
         <v>0</v>
@@ -1869,11 +1869,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="b">
         <v>0</v>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="b">
         <v>0</v>
@@ -1926,11 +1926,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="b">
         <v>0</v>
@@ -1945,11 +1945,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" t="b">
         <v>0</v>
@@ -1964,11 +1964,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81" t="b">
         <v>0</v>
@@ -1983,11 +1983,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D82" t="b">
         <v>0</v>
@@ -1997,16 +1997,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D83" t="b">
         <v>0</v>
@@ -2021,11 +2021,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D84" t="b">
         <v>0</v>
@@ -2040,11 +2040,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D85" t="b">
         <v>0</v>
@@ -2059,11 +2059,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" t="b">
         <v>0</v>
@@ -2078,11 +2078,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D87" t="b">
         <v>0</v>
@@ -2097,11 +2097,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" t="b">
         <v>0</v>
@@ -2116,11 +2116,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D89" t="b">
         <v>0</v>
@@ -2135,11 +2135,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" t="b">
         <v>0</v>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="b">
         <v>0</v>
@@ -2173,11 +2173,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D92" t="b">
         <v>0</v>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" t="b">
         <v>0</v>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="b">
         <v>0</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2268,11 +2268,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D97" t="b">
         <v>0</v>
@@ -2287,11 +2287,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="b">
         <v>0</v>
@@ -2306,11 +2306,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="b">
         <v>0</v>
@@ -2325,11 +2325,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" t="b">
         <v>0</v>
@@ -2344,11 +2344,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D101" t="b">
         <v>0</v>
@@ -2363,11 +2363,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D102" t="b">
         <v>0</v>
@@ -2377,16 +2377,16 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D103" t="b">
         <v>0</v>
@@ -2401,11 +2401,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D104" t="b">
         <v>0</v>
@@ -2420,11 +2420,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D105" t="b">
         <v>0</v>
@@ -2439,11 +2439,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D106" t="b">
         <v>0</v>
@@ -2458,11 +2458,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107" t="b">
         <v>0</v>
@@ -2477,11 +2477,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D108" t="b">
         <v>0</v>
@@ -2496,11 +2496,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" t="b">
         <v>0</v>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D110" t="b">
         <v>0</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2591,11 +2591,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="b">
         <v>0</v>
@@ -2610,11 +2610,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115" t="b">
         <v>0</v>
@@ -2629,11 +2629,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116" t="b">
         <v>0</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2724,11 +2724,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D121" t="b">
         <v>0</v>
@@ -2743,11 +2743,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D122" t="b">
         <v>0</v>
@@ -2757,16 +2757,16 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D123" t="b">
         <v>0</v>
@@ -2781,11 +2781,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D124" t="b">
         <v>0</v>
@@ -2800,11 +2800,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D125" t="b">
         <v>0</v>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D126" t="b">
         <v>0</v>
@@ -2838,11 +2838,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D127" t="b">
         <v>0</v>
@@ -2857,11 +2857,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D128" t="b">
         <v>0</v>
@@ -2876,11 +2876,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D129" t="b">
         <v>0</v>
@@ -2895,11 +2895,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" t="b">
         <v>0</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2952,11 +2952,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D133" t="b">
         <v>0</v>
@@ -2971,11 +2971,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D134" t="b">
         <v>0</v>
@@ -2990,11 +2990,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D135" t="b">
         <v>0</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3028,11 +3028,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D137" t="b">
         <v>0</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3066,11 +3066,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="b">
         <v>0</v>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D141" t="b">
         <v>0</v>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D142" t="b">
         <v>0</v>
@@ -3137,16 +3137,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D143" t="b">
         <v>0</v>
@@ -3161,11 +3161,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D144" t="b">
         <v>0</v>
@@ -3180,11 +3180,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D145" t="b">
         <v>0</v>
@@ -3199,11 +3199,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D146" t="b">
         <v>0</v>
@@ -3218,11 +3218,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D147" t="b">
         <v>0</v>
@@ -3237,11 +3237,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D148" t="b">
         <v>0</v>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -3275,11 +3275,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" t="b">
         <v>0</v>
@@ -3294,11 +3294,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151" t="b">
         <v>0</v>
@@ -3313,11 +3313,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" t="b">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -3351,11 +3351,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154" t="b">
         <v>0</v>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D155" t="b">
         <v>0</v>
@@ -3389,11 +3389,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D156" t="b">
         <v>0</v>
@@ -3408,11 +3408,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D157" t="b">
         <v>0</v>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="b">
         <v>0</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3465,11 +3465,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D160" t="b">
         <v>0</v>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -3503,11 +3503,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D162" t="b">
         <v>0</v>
@@ -3517,16 +3517,16 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D163" t="b">
         <v>0</v>
@@ -3541,11 +3541,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D164" t="b">
         <v>0</v>
@@ -3560,11 +3560,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D165" t="b">
         <v>0</v>
@@ -3579,11 +3579,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D166" t="b">
         <v>0</v>
@@ -3598,11 +3598,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D167" t="b">
         <v>0</v>
@@ -3617,11 +3617,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D168" t="b">
         <v>0</v>
@@ -3636,11 +3636,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D169" t="b">
         <v>0</v>
@@ -3655,11 +3655,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D170" t="b">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3712,11 +3712,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" t="b">
         <v>0</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3750,11 +3750,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D175" t="b">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D176" t="b">
         <v>0</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3807,11 +3807,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178" t="b">
         <v>0</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3864,11 +3864,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D181" t="b">
         <v>0</v>
@@ -3883,11 +3883,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D182" t="b">
         <v>0</v>
@@ -3897,16 +3897,16 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D183" t="b">
         <v>0</v>
@@ -3921,11 +3921,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D184" t="b">
         <v>0</v>
@@ -3940,11 +3940,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D185" t="b">
         <v>0</v>
@@ -3959,11 +3959,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D186" t="b">
         <v>0</v>
@@ -3978,11 +3978,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D187" t="b">
         <v>0</v>
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D188" t="b">
         <v>0</v>
@@ -4016,11 +4016,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D189" t="b">
         <v>0</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D190" t="b">
         <v>0</v>
@@ -4054,11 +4054,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D191" t="b">
         <v>0</v>
@@ -4073,11 +4073,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D192" t="b">
         <v>0</v>
@@ -4092,11 +4092,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D193" t="b">
         <v>0</v>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -4130,11 +4130,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" t="b">
         <v>0</v>
@@ -4149,11 +4149,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D196" t="b">
         <v>0</v>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -4187,11 +4187,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D198" t="b">
         <v>0</v>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -4244,11 +4244,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D201" t="b">
         <v>0</v>
@@ -4263,11 +4263,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D202" t="b">
         <v>0</v>
@@ -4277,16 +4277,16 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D203" t="b">
         <v>0</v>
@@ -4296,16 +4296,16 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D204" t="b">
         <v>0</v>
@@ -4320,11 +4320,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D205" t="b">
         <v>0</v>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D206" t="b">
         <v>0</v>
@@ -4358,11 +4358,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D207" t="b">
         <v>0</v>
@@ -4377,11 +4377,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D208" t="b">
         <v>0</v>
@@ -4396,11 +4396,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D209" t="b">
         <v>0</v>
@@ -4415,11 +4415,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D210" t="b">
         <v>0</v>
@@ -4434,11 +4434,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D211" t="b">
         <v>0</v>
@@ -4453,11 +4453,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D212" t="b">
         <v>0</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -4491,11 +4491,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D214" t="b">
         <v>0</v>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -4529,11 +4529,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D216" t="b">
         <v>0</v>
@@ -4548,11 +4548,11 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D217" t="b">
         <v>0</v>
@@ -4567,11 +4567,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D218" t="b">
         <v>0</v>
@@ -4586,11 +4586,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D219" t="b">
         <v>0</v>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D220" t="b">
         <v>0</v>
@@ -4624,11 +4624,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D221" t="b">
         <v>0</v>
@@ -4643,11 +4643,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222" t="b">
         <v>0</v>
@@ -4662,11 +4662,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D223" t="b">
         <v>0</v>
@@ -4676,16 +4676,16 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D224" t="b">
         <v>0</v>
@@ -4695,12 +4695,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -4719,11 +4719,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D226" t="b">
         <v>0</v>
@@ -4738,11 +4738,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D227" t="b">
         <v>0</v>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -4776,11 +4776,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229" t="b">
         <v>0</v>
@@ -4795,16 +4795,18 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C230" t="n">
         <v>2</v>
       </c>
       <c r="D230" t="b">
-        <v>0</v>
-      </c>
-      <c r="E230" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E230" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4814,11 +4816,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231" t="b">
         <v>0</v>
@@ -4833,11 +4835,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232" t="b">
         <v>0</v>
@@ -4852,11 +4854,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D233" t="b">
         <v>0</v>
@@ -4871,7 +4873,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4890,7 +4892,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4909,11 +4911,11 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D236" t="b">
         <v>0</v>
@@ -4928,11 +4930,11 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237" t="b">
         <v>0</v>
@@ -4947,11 +4949,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D238" t="b">
         <v>0</v>
@@ -4966,11 +4968,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239" t="b">
         <v>0</v>
@@ -4985,11 +4987,11 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D240" t="b">
         <v>0</v>
@@ -5004,11 +5006,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D241" t="b">
         <v>0</v>
@@ -5023,11 +5025,11 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D242" t="b">
         <v>0</v>
@@ -5042,11 +5044,11 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D243" t="b">
         <v>0</v>
@@ -5056,16 +5058,16 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D244" t="b">
         <v>0</v>
@@ -5075,12 +5077,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -5099,11 +5101,11 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D246" t="b">
         <v>0</v>
@@ -5118,11 +5120,11 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D247" t="b">
         <v>0</v>
@@ -5137,11 +5139,11 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D248" t="b">
         <v>0</v>
@@ -5156,11 +5158,11 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249" t="b">
         <v>0</v>
@@ -5175,11 +5177,11 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D250" t="b">
         <v>0</v>
@@ -5194,11 +5196,11 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D251" t="b">
         <v>0</v>
@@ -5213,7 +5215,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -5232,11 +5234,11 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D253" t="b">
         <v>0</v>
@@ -5251,11 +5253,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D254" t="b">
         <v>0</v>
@@ -5270,11 +5272,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D255" t="b">
         <v>0</v>
@@ -5289,11 +5291,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D256" t="b">
         <v>0</v>
@@ -5308,11 +5310,11 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D257" t="b">
         <v>0</v>
@@ -5327,11 +5329,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D258" t="b">
         <v>0</v>
@@ -5346,11 +5348,11 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D259" t="b">
         <v>0</v>
@@ -5365,11 +5367,11 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D260" t="b">
         <v>0</v>
@@ -5384,11 +5386,11 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D261" t="b">
         <v>0</v>
@@ -5403,11 +5405,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D262" t="b">
         <v>0</v>
@@ -5422,11 +5424,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D263" t="b">
         <v>0</v>
@@ -5436,16 +5438,16 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D264" t="b">
         <v>0</v>
@@ -5455,12 +5457,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -5479,11 +5481,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D266" t="b">
         <v>0</v>
@@ -5498,11 +5500,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D267" t="b">
         <v>0</v>
@@ -5517,7 +5519,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -5536,11 +5538,11 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D269" t="b">
         <v>0</v>
@@ -5555,7 +5557,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -5574,7 +5576,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -5593,11 +5595,11 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D272" t="b">
         <v>0</v>
@@ -5612,11 +5614,11 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D273" t="b">
         <v>0</v>
@@ -5631,11 +5633,11 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D274" t="b">
         <v>0</v>
@@ -5650,7 +5652,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -5669,7 +5671,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -5688,11 +5690,11 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D277" t="b">
         <v>0</v>
@@ -5707,11 +5709,11 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D278" t="b">
         <v>0</v>
@@ -5726,11 +5728,11 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D279" t="b">
         <v>0</v>
@@ -5745,7 +5747,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -5764,11 +5766,11 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D281" t="b">
         <v>0</v>
@@ -5783,11 +5785,11 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D282" t="b">
         <v>0</v>
@@ -5802,11 +5804,11 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D283" t="b">
         <v>0</v>
@@ -5816,16 +5818,16 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D284" t="b">
         <v>0</v>
@@ -5835,16 +5837,16 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D285" t="b">
         <v>0</v>
@@ -5859,11 +5861,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D286" t="b">
         <v>0</v>
@@ -5878,11 +5880,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D287" t="b">
         <v>0</v>
@@ -5897,11 +5899,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D288" t="b">
         <v>0</v>
@@ -5916,11 +5918,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D289" t="b">
         <v>0</v>
@@ -5935,11 +5937,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D290" t="b">
         <v>0</v>
@@ -5954,11 +5956,11 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D291" t="b">
         <v>0</v>
@@ -5973,11 +5975,11 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D292" t="b">
         <v>0</v>
@@ -5992,11 +5994,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D293" t="b">
         <v>0</v>
@@ -6011,11 +6013,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D294" t="b">
         <v>0</v>
@@ -6030,11 +6032,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D295" t="b">
         <v>0</v>
@@ -6049,7 +6051,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -6068,11 +6070,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D297" t="b">
         <v>0</v>
@@ -6087,11 +6089,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D298" t="b">
         <v>0</v>
@@ -6106,11 +6108,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D299" t="b">
         <v>0</v>
@@ -6125,11 +6127,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D300" t="b">
         <v>0</v>
@@ -6144,7 +6146,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -6163,7 +6165,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -6182,11 +6184,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D303" t="b">
         <v>0</v>
@@ -6201,11 +6203,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D304" t="b">
         <v>0</v>
@@ -6215,12 +6217,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -6234,16 +6236,16 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D306" t="b">
         <v>0</v>
@@ -6258,11 +6260,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D307" t="b">
         <v>0</v>
@@ -6277,11 +6279,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D308" t="b">
         <v>0</v>
@@ -6296,11 +6298,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D309" t="b">
         <v>0</v>
@@ -6315,11 +6317,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D310" t="b">
         <v>0</v>
@@ -6334,7 +6336,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -6353,11 +6355,11 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D312" t="b">
         <v>0</v>
@@ -6372,7 +6374,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -6391,11 +6393,11 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D314" t="b">
         <v>0</v>
@@ -6410,11 +6412,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D315" t="b">
         <v>0</v>
@@ -6429,7 +6431,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -6448,11 +6450,11 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D317" t="b">
         <v>0</v>
@@ -6467,11 +6469,11 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D318" t="b">
         <v>0</v>
@@ -6486,7 +6488,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -6505,7 +6507,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -6524,11 +6526,11 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D321" t="b">
         <v>0</v>
@@ -6543,11 +6545,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D322" t="b">
         <v>0</v>
@@ -6562,7 +6564,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -6581,11 +6583,11 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D324" t="b">
         <v>0</v>
@@ -6595,16 +6597,16 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D325" t="b">
         <v>0</v>
@@ -6614,12 +6616,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -6638,11 +6640,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D327" t="b">
         <v>0</v>
@@ -6657,11 +6659,11 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D328" t="b">
         <v>0</v>
@@ -6676,11 +6678,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D329" t="b">
         <v>0</v>
@@ -6695,11 +6697,11 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D330" t="b">
         <v>0</v>
@@ -6714,11 +6716,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D331" t="b">
         <v>0</v>
@@ -6733,11 +6735,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D332" t="b">
         <v>0</v>
@@ -6752,11 +6754,11 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D333" t="b">
         <v>0</v>
@@ -6771,11 +6773,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D334" t="b">
         <v>0</v>
@@ -6790,7 +6792,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -6809,11 +6811,11 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D336" t="b">
         <v>0</v>
@@ -6828,11 +6830,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D337" t="b">
         <v>0</v>
@@ -6847,11 +6849,11 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D338" t="b">
         <v>0</v>
@@ -6866,7 +6868,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -6885,11 +6887,11 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D340" t="b">
         <v>0</v>
@@ -6904,11 +6906,11 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D341" t="b">
         <v>0</v>
@@ -6923,7 +6925,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -6942,11 +6944,11 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D343" t="b">
         <v>0</v>
@@ -6961,11 +6963,11 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D344" t="b">
         <v>0</v>
@@ -6980,11 +6982,11 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D345" t="b">
         <v>0</v>
@@ -6994,16 +6996,16 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D346" t="b">
         <v>0</v>
@@ -7013,16 +7015,16 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D347" t="b">
         <v>0</v>
@@ -7037,11 +7039,11 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D348" t="b">
         <v>0</v>
@@ -7056,11 +7058,11 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D349" t="b">
         <v>0</v>
@@ -7075,11 +7077,11 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D350" t="b">
         <v>0</v>
@@ -7094,11 +7096,11 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D351" t="b">
         <v>0</v>
@@ -7113,11 +7115,11 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D352" t="b">
         <v>0</v>
@@ -7132,7 +7134,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -7151,11 +7153,11 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D354" t="b">
         <v>0</v>
@@ -7170,11 +7172,11 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D355" t="b">
         <v>0</v>
@@ -7189,7 +7191,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -7208,11 +7210,11 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D357" t="b">
         <v>0</v>
@@ -7227,11 +7229,11 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D358" t="b">
         <v>0</v>
@@ -7246,11 +7248,11 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D359" t="b">
         <v>0</v>
@@ -7265,11 +7267,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D360" t="b">
         <v>0</v>
@@ -7284,11 +7286,11 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D361" t="b">
         <v>0</v>
@@ -7303,11 +7305,11 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D362" t="b">
         <v>0</v>
@@ -7322,11 +7324,11 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D363" t="b">
         <v>0</v>
@@ -7341,11 +7343,11 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D364" t="b">
         <v>0</v>
@@ -7360,11 +7362,11 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D365" t="b">
         <v>0</v>
@@ -7379,11 +7381,11 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D366" t="b">
         <v>0</v>
@@ -7393,16 +7395,16 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D367" t="b">
         <v>0</v>
@@ -7412,16 +7414,16 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D368" t="b">
         <v>0</v>
@@ -7436,7 +7438,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -7455,11 +7457,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D370" t="b">
         <v>0</v>
@@ -7474,7 +7476,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -7493,7 +7495,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -7512,11 +7514,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D373" t="b">
         <v>0</v>
@@ -7531,11 +7533,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D374" t="b">
         <v>0</v>
@@ -7550,11 +7552,11 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D375" t="b">
         <v>0</v>
@@ -7569,7 +7571,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -7588,7 +7590,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -7607,11 +7609,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D378" t="b">
         <v>0</v>
@@ -7626,11 +7628,11 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D379" t="b">
         <v>0</v>
@@ -7645,7 +7647,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -7664,7 +7666,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -7683,7 +7685,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -7702,7 +7704,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -7721,7 +7723,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -7740,7 +7742,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -7759,11 +7761,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D386" t="b">
         <v>0</v>
@@ -7773,16 +7775,16 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D387" t="b">
         <v>0</v>
@@ -7792,16 +7794,16 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D388" t="b">
         <v>0</v>
@@ -7816,11 +7818,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D389" t="b">
         <v>0</v>
@@ -7835,11 +7837,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D390" t="b">
         <v>0</v>
@@ -7854,11 +7856,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D391" t="b">
         <v>0</v>
@@ -7873,7 +7875,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -7892,11 +7894,11 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D393" t="b">
         <v>0</v>
@@ -7911,7 +7913,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -7930,7 +7932,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -7949,7 +7951,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -7968,11 +7970,11 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D397" t="b">
         <v>0</v>
@@ -7987,11 +7989,11 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D398" t="b">
         <v>0</v>
@@ -8006,7 +8008,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -8025,11 +8027,11 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D400" t="b">
         <v>0</v>
@@ -8044,11 +8046,11 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D401" t="b">
         <v>0</v>
@@ -8063,11 +8065,11 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D402" t="b">
         <v>0</v>
@@ -8082,7 +8084,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -8101,7 +8103,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -8120,11 +8122,11 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D405" t="b">
         <v>0</v>
@@ -8139,11 +8141,11 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D406" t="b">
         <v>0</v>
@@ -8153,16 +8155,16 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D407" t="b">
         <v>0</v>
@@ -8172,16 +8174,16 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D408" t="b">
         <v>0</v>
@@ -8196,11 +8198,11 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D409" t="b">
         <v>0</v>
@@ -8215,11 +8217,11 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D410" t="b">
         <v>0</v>
@@ -8234,11 +8236,11 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D411" t="b">
         <v>0</v>
@@ -8253,11 +8255,11 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D412" t="b">
         <v>0</v>
@@ -8272,11 +8274,11 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D413" t="b">
         <v>0</v>
@@ -8291,11 +8293,11 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D414" t="b">
         <v>0</v>
@@ -8310,7 +8312,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -8329,7 +8331,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -8348,7 +8350,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -8367,7 +8369,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -8386,11 +8388,11 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D419" t="b">
         <v>0</v>
@@ -8405,7 +8407,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -8424,11 +8426,11 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D421" t="b">
         <v>0</v>
@@ -8443,11 +8445,11 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D422" t="b">
         <v>0</v>
@@ -8462,11 +8464,11 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D423" t="b">
         <v>0</v>
@@ -8481,7 +8483,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -8500,11 +8502,11 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D425" t="b">
         <v>0</v>
@@ -8519,11 +8521,11 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D426" t="b">
         <v>0</v>
@@ -8538,11 +8540,11 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D427" t="b">
         <v>0</v>
@@ -8552,16 +8554,16 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D428" t="b">
         <v>0</v>
@@ -8571,16 +8573,16 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D429" t="b">
         <v>0</v>
@@ -8595,11 +8597,11 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D430" t="b">
         <v>0</v>
@@ -8614,11 +8616,11 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D431" t="b">
         <v>0</v>
@@ -8633,7 +8635,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -8652,11 +8654,11 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D433" t="b">
         <v>0</v>
@@ -8671,11 +8673,11 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D434" t="b">
         <v>0</v>
@@ -8690,11 +8692,11 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D435" t="b">
         <v>0</v>
@@ -8709,11 +8711,11 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D436" t="b">
         <v>0</v>
@@ -8728,11 +8730,11 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D437" t="b">
         <v>0</v>
@@ -8747,11 +8749,11 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D438" t="b">
         <v>0</v>
@@ -8766,7 +8768,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -8785,11 +8787,11 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D440" t="b">
         <v>0</v>
@@ -8804,11 +8806,11 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D441" t="b">
         <v>0</v>
@@ -8823,11 +8825,11 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D442" t="b">
         <v>0</v>
@@ -8842,11 +8844,11 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D443" t="b">
         <v>0</v>
@@ -8861,11 +8863,11 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D444" t="b">
         <v>0</v>
@@ -8880,7 +8882,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -8899,11 +8901,11 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D446" t="b">
         <v>0</v>
@@ -8918,11 +8920,11 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D447" t="b">
         <v>0</v>
@@ -8932,16 +8934,16 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D448" t="b">
         <v>0</v>
@@ -8951,16 +8953,16 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D449" t="b">
         <v>0</v>
@@ -8975,11 +8977,11 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D450" t="b">
         <v>0</v>
@@ -8994,11 +8996,11 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D451" t="b">
         <v>0</v>
@@ -9013,11 +9015,11 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D452" t="b">
         <v>0</v>
@@ -9032,7 +9034,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -9051,11 +9053,11 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D454" t="b">
         <v>0</v>
@@ -9070,7 +9072,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -9089,11 +9091,11 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D456" t="b">
         <v>0</v>
@@ -9108,7 +9110,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -9127,11 +9129,11 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D458" t="b">
         <v>0</v>
@@ -9146,11 +9148,11 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D459" t="b">
         <v>0</v>
@@ -9165,11 +9167,11 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D460" t="b">
         <v>0</v>
@@ -9184,11 +9186,11 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D461" t="b">
         <v>0</v>
@@ -9203,11 +9205,11 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D462" t="b">
         <v>0</v>
@@ -9222,11 +9224,11 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D463" t="b">
         <v>0</v>
@@ -9241,7 +9243,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -9260,11 +9262,11 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D465" t="b">
         <v>0</v>
@@ -9279,11 +9281,11 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D466" t="b">
         <v>0</v>
@@ -9298,11 +9300,11 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D467" t="b">
         <v>0</v>
@@ -9312,16 +9314,16 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D468" t="b">
         <v>0</v>
@@ -9331,16 +9333,16 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D469" t="b">
         <v>0</v>
@@ -9355,11 +9357,11 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D470" t="b">
         <v>0</v>
@@ -9374,11 +9376,11 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D471" t="b">
         <v>0</v>
@@ -9393,7 +9395,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -9412,11 +9414,11 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D473" t="b">
         <v>0</v>
@@ -9431,11 +9433,11 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D474" t="b">
         <v>0</v>
@@ -9450,7 +9452,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -9469,11 +9471,11 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D476" t="b">
         <v>0</v>
@@ -9488,11 +9490,11 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D477" t="b">
         <v>0</v>
@@ -9507,7 +9509,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -9526,7 +9528,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -9545,11 +9547,11 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D480" t="b">
         <v>0</v>
@@ -9564,11 +9566,11 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D481" t="b">
         <v>0</v>
@@ -9583,7 +9585,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -9602,7 +9604,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -9621,7 +9623,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -9640,11 +9642,11 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D485" t="b">
         <v>0</v>
@@ -9659,11 +9661,11 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D486" t="b">
         <v>0</v>
@@ -9678,11 +9680,11 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D487" t="b">
         <v>0</v>
@@ -9692,16 +9694,16 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D488" t="b">
         <v>0</v>
@@ -9711,16 +9713,16 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D489" t="b">
         <v>0</v>
@@ -9735,11 +9737,11 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D490" t="b">
         <v>0</v>
@@ -9754,11 +9756,11 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D491" t="b">
         <v>0</v>
@@ -9773,11 +9775,11 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D492" t="b">
         <v>0</v>
@@ -9792,11 +9794,11 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D493" t="b">
         <v>0</v>
@@ -9811,7 +9813,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -9830,11 +9832,11 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D495" t="b">
         <v>0</v>
@@ -9849,11 +9851,11 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D496" t="b">
         <v>0</v>
@@ -9868,11 +9870,11 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D497" t="b">
         <v>0</v>
@@ -9887,11 +9889,11 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D498" t="b">
         <v>0</v>
@@ -9906,7 +9908,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -9925,7 +9927,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -9944,11 +9946,11 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D501" t="b">
         <v>0</v>
@@ -9963,11 +9965,11 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D502" t="b">
         <v>0</v>
@@ -9982,7 +9984,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -10001,7 +10003,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -10020,7 +10022,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -10039,11 +10041,11 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D506" t="b">
         <v>0</v>
@@ -10058,11 +10060,11 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D507" t="b">
         <v>0</v>
@@ -10072,16 +10074,16 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D508" t="b">
         <v>0</v>
@@ -10091,16 +10093,16 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D509" t="b">
         <v>0</v>
@@ -10115,11 +10117,11 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D510" t="b">
         <v>0</v>
@@ -10134,11 +10136,11 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D511" t="b">
         <v>0</v>
@@ -10153,11 +10155,11 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D512" t="b">
         <v>0</v>
@@ -10172,11 +10174,11 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D513" t="b">
         <v>0</v>
@@ -10191,11 +10193,11 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D514" t="b">
         <v>0</v>
@@ -10210,11 +10212,11 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D515" t="b">
         <v>0</v>
@@ -10229,11 +10231,11 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D516" t="b">
         <v>0</v>
@@ -10248,11 +10250,11 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D517" t="b">
         <v>0</v>
@@ -10267,11 +10269,11 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D518" t="b">
         <v>0</v>
@@ -10286,11 +10288,11 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D519" t="b">
         <v>0</v>
@@ -10305,11 +10307,11 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D520" t="b">
         <v>0</v>
@@ -10324,11 +10326,11 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D521" t="b">
         <v>0</v>
@@ -10343,11 +10345,11 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D522" t="b">
         <v>0</v>
@@ -10362,11 +10364,11 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D523" t="b">
         <v>0</v>
@@ -10381,7 +10383,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -10400,7 +10402,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -10419,7 +10421,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -10438,11 +10440,11 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D527" t="b">
         <v>0</v>
@@ -10457,11 +10459,11 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D528" t="b">
         <v>0</v>
@@ -10471,16 +10473,16 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D529" t="b">
         <v>0</v>
@@ -10490,16 +10492,16 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D530" t="b">
         <v>0</v>
@@ -10514,11 +10516,11 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D531" t="b">
         <v>0</v>
@@ -10533,11 +10535,11 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D532" t="b">
         <v>0</v>
@@ -10552,11 +10554,11 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D533" t="b">
         <v>0</v>
@@ -10571,11 +10573,11 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D534" t="b">
         <v>0</v>
@@ -10590,11 +10592,11 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D535" t="b">
         <v>0</v>
@@ -10609,11 +10611,11 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D536" t="b">
         <v>0</v>
@@ -10628,11 +10630,11 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D537" t="b">
         <v>0</v>
@@ -10647,11 +10649,11 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D538" t="b">
         <v>0</v>
@@ -10666,11 +10668,11 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D539" t="b">
         <v>0</v>
@@ -10685,11 +10687,11 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D540" t="b">
         <v>0</v>
@@ -10704,11 +10706,11 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D541" t="b">
         <v>0</v>
@@ -10723,11 +10725,11 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D542" t="b">
         <v>0</v>
@@ -10742,11 +10744,11 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D543" t="b">
         <v>0</v>
@@ -10761,11 +10763,11 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D544" t="b">
         <v>0</v>
@@ -10780,11 +10782,11 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D545" t="b">
         <v>0</v>
@@ -10799,7 +10801,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -10818,7 +10820,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -10837,11 +10839,11 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D548" t="b">
         <v>0</v>
@@ -10851,16 +10853,16 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D549" t="b">
         <v>0</v>
@@ -10870,16 +10872,16 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D550" t="b">
         <v>0</v>
@@ -10894,11 +10896,11 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D551" t="b">
         <v>0</v>
@@ -10913,11 +10915,11 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D552" t="b">
         <v>0</v>
@@ -10932,7 +10934,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -10951,11 +10953,11 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C554" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D554" t="b">
         <v>0</v>
@@ -10970,16 +10972,18 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C555" t="n">
         <v>2</v>
       </c>
       <c r="D555" t="b">
-        <v>0</v>
-      </c>
-      <c r="E555" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E555" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -10989,11 +10993,11 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C556" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D556" t="b">
         <v>0</v>
@@ -11008,11 +11012,11 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C557" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D557" t="b">
         <v>0</v>
@@ -11027,11 +11031,11 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C558" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D558" t="b">
         <v>0</v>
@@ -11046,11 +11050,11 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C559" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D559" t="b">
         <v>0</v>
@@ -11065,11 +11069,11 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C560" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D560" t="b">
         <v>0</v>
@@ -11084,11 +11088,11 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C561" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D561" t="b">
         <v>0</v>
@@ -11103,11 +11107,11 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C562" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D562" t="b">
         <v>0</v>
@@ -11122,11 +11126,11 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D563" t="b">
         <v>0</v>
@@ -11141,7 +11145,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -11160,7 +11164,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -11179,7 +11183,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -11198,11 +11202,11 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D567" t="b">
         <v>0</v>
@@ -11217,11 +11221,11 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C568" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D568" t="b">
         <v>0</v>
@@ -11231,16 +11235,16 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C569" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D569" t="b">
         <v>0</v>
@@ -11250,12 +11254,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -11274,11 +11278,11 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D571" t="b">
         <v>0</v>
@@ -11293,11 +11297,11 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C572" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D572" t="b">
         <v>0</v>
@@ -11312,11 +11316,11 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D573" t="b">
         <v>0</v>
@@ -11331,11 +11335,11 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D574" t="b">
         <v>0</v>
@@ -11350,7 +11354,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -11369,11 +11373,11 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C576" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D576" t="b">
         <v>0</v>
@@ -11388,11 +11392,11 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C577" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D577" t="b">
         <v>0</v>
@@ -11407,11 +11411,11 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C578" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D578" t="b">
         <v>0</v>
@@ -11426,11 +11430,11 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C579" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D579" t="b">
         <v>0</v>
@@ -11445,11 +11449,11 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C580" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D580" t="b">
         <v>0</v>
@@ -11464,7 +11468,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -11483,11 +11487,11 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C582" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D582" t="b">
         <v>0</v>
@@ -11502,11 +11506,11 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C583" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D583" t="b">
         <v>0</v>
@@ -11521,11 +11525,11 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C584" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D584" t="b">
         <v>0</v>
@@ -11540,7 +11544,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -11559,7 +11563,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -11578,7 +11582,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -11597,11 +11601,11 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C588" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D588" t="b">
         <v>0</v>
@@ -11616,11 +11620,11 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C589" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D589" t="b">
         <v>0</v>
@@ -11630,16 +11634,16 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C590" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D590" t="b">
         <v>0</v>
@@ -11649,16 +11653,16 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C591" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D591" t="b">
         <v>0</v>
@@ -11673,11 +11677,11 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C592" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D592" t="b">
         <v>0</v>
@@ -11692,11 +11696,11 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C593" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D593" t="b">
         <v>0</v>
@@ -11711,11 +11715,11 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C594" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D594" t="b">
         <v>0</v>
@@ -11730,7 +11734,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -11749,11 +11753,11 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D596" t="b">
         <v>0</v>
@@ -11768,11 +11772,11 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C597" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D597" t="b">
         <v>0</v>
@@ -11787,11 +11791,11 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C598" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D598" t="b">
         <v>0</v>
@@ -11806,11 +11810,11 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D599" t="b">
         <v>0</v>
@@ -11825,11 +11829,11 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D600" t="b">
         <v>0</v>
@@ -11844,7 +11848,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -11863,7 +11867,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -11882,11 +11886,11 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C603" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D603" t="b">
         <v>0</v>
@@ -11901,7 +11905,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -11920,7 +11924,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -11939,11 +11943,11 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D606" t="b">
         <v>0</v>
@@ -11958,11 +11962,11 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C607" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D607" t="b">
         <v>0</v>
@@ -11977,11 +11981,11 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D608" t="b">
         <v>0</v>
@@ -11996,11 +12000,11 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D609" t="b">
         <v>0</v>
@@ -12010,16 +12014,16 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D610" t="b">
         <v>0</v>
@@ -12029,16 +12033,16 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C611" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D611" t="b">
         <v>0</v>
@@ -12053,11 +12057,11 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D612" t="b">
         <v>0</v>
@@ -12072,11 +12076,11 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D613" t="b">
         <v>0</v>
@@ -12091,11 +12095,11 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D614" t="b">
         <v>0</v>
@@ -12110,11 +12114,11 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D615" t="b">
         <v>0</v>
@@ -12129,11 +12133,11 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C616" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D616" t="b">
         <v>0</v>
@@ -12148,7 +12152,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -12167,7 +12171,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -12186,11 +12190,11 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C619" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D619" t="b">
         <v>0</v>
@@ -12205,7 +12209,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -12224,11 +12228,11 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D621" t="b">
         <v>0</v>
@@ -12243,11 +12247,11 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D622" t="b">
         <v>0</v>
@@ -12262,11 +12266,11 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D623" t="b">
         <v>0</v>
@@ -12281,11 +12285,11 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C624" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D624" t="b">
         <v>0</v>
@@ -12300,11 +12304,11 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C625" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D625" t="b">
         <v>0</v>
@@ -12319,11 +12323,11 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C626" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D626" t="b">
         <v>0</v>
@@ -12338,7 +12342,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -12357,11 +12361,11 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C628" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D628" t="b">
         <v>0</v>
@@ -12376,11 +12380,11 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C629" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D629" t="b">
         <v>0</v>
@@ -12390,16 +12394,16 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C630" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D630" t="b">
         <v>0</v>
@@ -12409,16 +12413,16 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C631" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D631" t="b">
         <v>0</v>
@@ -12433,11 +12437,11 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C632" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D632" t="b">
         <v>0</v>
@@ -12452,11 +12456,11 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C633" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D633" t="b">
         <v>0</v>
@@ -12471,11 +12475,11 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C634" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D634" t="b">
         <v>0</v>
@@ -12490,11 +12494,11 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C635" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D635" t="b">
         <v>0</v>
@@ -12509,11 +12513,11 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D636" t="b">
         <v>0</v>
@@ -12528,11 +12532,11 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="C637" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D637" t="b">
         <v>0</v>
@@ -12547,11 +12551,11 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C638" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D638" t="b">
         <v>0</v>
@@ -12566,11 +12570,11 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>LOLB</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C639" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D639" t="b">
         <v>0</v>
@@ -12585,7 +12589,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -12604,7 +12608,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>LOLB</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -12623,7 +12627,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -12642,11 +12646,11 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D643" t="b">
         <v>0</v>
@@ -12661,11 +12665,11 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C644" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D644" t="b">
         <v>0</v>
@@ -12680,11 +12684,11 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="C645" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D645" t="b">
         <v>0</v>
@@ -12699,11 +12703,11 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>ROLB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="C646" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D646" t="b">
         <v>0</v>
@@ -12718,7 +12722,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RG</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -12737,11 +12741,11 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ROLB</t>
         </is>
       </c>
       <c r="C648" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D648" t="b">
         <v>0</v>
@@ -12756,11 +12760,11 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D649" t="b">
         <v>0</v>
@@ -12775,16 +12779,54 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>4</v>
+      </c>
+      <c r="D650" t="b">
+        <v>0</v>
+      </c>
+      <c r="E650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>4</v>
+      </c>
+      <c r="D651" t="b">
+        <v>0</v>
+      </c>
+      <c r="E651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
           <t>WR</t>
         </is>
       </c>
-      <c r="C650" t="n">
+      <c r="C652" t="n">
         <v>6</v>
       </c>
-      <c r="D650" t="b">
-        <v>0</v>
-      </c>
-      <c r="E650" t="inlineStr"/>
+      <c r="D652" t="b">
+        <v>0</v>
+      </c>
+      <c r="E652" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
